--- a/data/trans_orig/P04A_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P04A_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si la vivienda que ocupan es de propiedad o de alquiler en 2023</t>
+          <t>Población según si la vivienda que ocupan es de propiedad o de alquiler en 2023 (tasa de respuesta: 99,63%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3625</t>
+          <t>3540</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29900</t>
+          <t>31606</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18710</t>
+          <t>17149</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5832</t>
+          <t>6450</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35462</t>
+          <t>35328</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1604</t>
+          <t>1549</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23889</t>
+          <t>23804</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>2953</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15692</t>
+          <t>14965</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7200</t>
+          <t>6846</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33140</t>
+          <t>32551</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18187</t>
+          <t>18794</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>54366</t>
+          <t>52252</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>44014</t>
+          <t>45491</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>83656</t>
+          <t>86031</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>69770</t>
+          <t>70754</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>122107</t>
+          <t>123023</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,68%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13475</t>
+          <t>13057</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>54530</t>
+          <t>55378</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4412</t>
+          <t>3559</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21941</t>
+          <t>21480</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21881</t>
+          <t>22894</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>65459</t>
+          <t>62659</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,01%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>69229</t>
+          <t>71613</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>131270</t>
+          <t>131093</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>53943</t>
+          <t>52874</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>92630</t>
+          <t>91617</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>134405</t>
+          <t>136740</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>205494</t>
+          <t>206464</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,68%</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>174622</t>
+          <t>175975</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>242367</t>
+          <t>239282</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>45,46%</t>
+          <t>45,81%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>63,09%</t>
+          <t>62,29%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>131154</t>
+          <t>130564</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>178036</t>
+          <t>178089</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>41,9%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>57,14%</t>
+          <t>57,15%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>319877</t>
+          <t>322851</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>402663</t>
+          <t>404686</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1380,12 +1380,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>45,98%</t>
+          <t>46,4%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>57,88%</t>
+          <t>58,17%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1385</t>
+          <t>1678</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19515</t>
+          <t>19741</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>872</t>
+          <t>803</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8233</t>
+          <t>9098</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4264</t>
+          <t>3811</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>21926</t>
+          <t>21060</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6028</t>
+          <t>6311</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>22697</t>
+          <t>22766</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5005</t>
+          <t>4880</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>20364</t>
+          <t>21745</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>13742</t>
+          <t>14358</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>37021</t>
+          <t>37534</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>76943</t>
+          <t>76181</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>119644</t>
+          <t>120469</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>99965</t>
+          <t>98913</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>306123</t>
+          <t>297086</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>60,05%</t>
+          <t>58,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>190610</t>
+          <t>194855</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>421791</t>
+          <t>431508</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,27%</t>
+          <t>46,31%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>20327</t>
+          <t>19984</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>51992</t>
+          <t>49700</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18916</t>
+          <t>18526</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>45356</t>
+          <t>45624</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>44247</t>
+          <t>43652</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>89262</t>
+          <t>85491</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,18%</t>
         </is>
       </c>
     </row>
@@ -1977,12 +1977,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>102877</t>
+          <t>103370</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>150738</t>
+          <t>150503</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2012,12 +2012,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>81815</t>
+          <t>89781</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>172921</t>
+          <t>171671</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>203695</t>
+          <t>200014</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>304990</t>
+          <t>305831</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,82%</t>
         </is>
       </c>
     </row>
@@ -2090,12 +2090,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>122814</t>
+          <t>124107</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>171629</t>
+          <t>172061</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>96306</t>
+          <t>96171</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>195731</t>
+          <t>198665</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>230293</t>
+          <t>225550</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>349559</t>
+          <t>348320</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>37,38%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>1036</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11078</t>
+          <t>11070</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1131</t>
+          <t>1551</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8769</t>
+          <t>9358</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3708</t>
+          <t>3478</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>17183</t>
+          <t>16021</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9200</t>
+          <t>8845</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23716</t>
+          <t>24037</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5958</t>
+          <t>5744</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18155</t>
+          <t>17171</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17956</t>
+          <t>17948</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>36447</t>
+          <t>37237</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>63525</t>
+          <t>62740</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>97268</t>
+          <t>98561</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>72027</t>
+          <t>72862</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>231651</t>
+          <t>242644</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>41,13%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>149371</t>
+          <t>148702</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>337345</t>
+          <t>335105</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>29,89%</t>
         </is>
       </c>
     </row>
@@ -2659,12 +2659,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>25912</t>
+          <t>25357</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>49726</t>
+          <t>50397</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>17184</t>
+          <t>16515</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>34983</t>
+          <t>35090</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2709,12 +2709,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>48632</t>
+          <t>46499</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>77010</t>
+          <t>75910</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2744,12 +2744,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -2772,12 +2772,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>229900</t>
+          <t>231439</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>276472</t>
+          <t>276578</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2787,12 +2787,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>43,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>52,03%</t>
+          <t>52,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>201570</t>
+          <t>196840</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>302965</t>
+          <t>301627</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>51,36%</t>
+          <t>51,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>450542</t>
+          <t>446589</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>563563</t>
+          <t>563267</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>39,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>50,26%</t>
+          <t>50,24%</t>
         </is>
       </c>
     </row>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>124647</t>
+          <t>124266</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>166747</t>
+          <t>164793</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2900,12 +2900,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2920,12 +2920,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>114294</t>
+          <t>118979</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>181447</t>
+          <t>181819</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>260557</t>
+          <t>258218</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>334484</t>
+          <t>335110</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,89%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1144</t>
+          <t>1126</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>14844</t>
+          <t>14134</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2055</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8715</t>
+          <t>8238</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4543</t>
+          <t>4213</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>17870</t>
+          <t>18320</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2709</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>17040</t>
+          <t>17811</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>4808</t>
+          <t>4491</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>13879</t>
+          <t>14164</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>8783</t>
+          <t>8720</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>25562</t>
+          <t>26084</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -3341,12 +3341,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>27631</t>
+          <t>25337</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>106673</t>
+          <t>102970</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3376,12 +3376,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>39379</t>
+          <t>39843</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>69965</t>
+          <t>72184</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3411,12 +3411,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>74065</t>
+          <t>74499</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>155138</t>
+          <t>159317</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,98%</t>
         </is>
       </c>
     </row>
@@ -3454,12 +3454,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>11026</t>
+          <t>12246</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>46328</t>
+          <t>47231</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3469,12 +3469,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>17615</t>
+          <t>18121</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>33063</t>
+          <t>33737</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>31381</t>
+          <t>31863</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>71157</t>
+          <t>70750</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -3567,12 +3567,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>99401</t>
+          <t>99361</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>324222</t>
+          <t>323545</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>36,44%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>196925</t>
+          <t>198113</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>259730</t>
+          <t>258643</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>259166</t>
+          <t>274364</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>557596</t>
+          <t>559219</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>35,03%</t>
         </is>
       </c>
     </row>
@@ -3680,12 +3680,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>410719</t>
+          <t>413505</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>732147</t>
+          <t>743521</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>46,58%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>82,47%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>355595</t>
+          <t>356433</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>435563</t>
+          <t>429311</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
+          <t>50,31%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>61,48%</t>
+          <t>60,6%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>797736</t>
+          <t>798786</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1210583</t>
+          <t>1194539</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>49,98%</t>
+          <t>50,04%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>74,83%</t>
         </is>
       </c>
     </row>
@@ -3910,62 +3910,62 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>8969</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>0,03%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>1205</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
           <t>161</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>8198</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>3638</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
         <is>
           <t>0,03%</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>1,47%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>1205</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>3979</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>0,03%</t>
-        </is>
-      </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>8797</t>
+          <t>9397</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -4023,12 +4023,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2427</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>11010</t>
+          <t>11230</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4038,12 +4038,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4058,12 +4058,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>3777</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>11556</t>
+          <t>11688</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4093,12 +4093,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>7939</t>
+          <t>7196</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>19031</t>
+          <t>18836</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -4136,12 +4136,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>22851</t>
+          <t>21951</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>43284</t>
+          <t>42159</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4151,12 +4151,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>21925</t>
+          <t>21560</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>37500</t>
+          <t>36998</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>48360</t>
+          <t>48829</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>73178</t>
+          <t>73534</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,65%</t>
         </is>
       </c>
     </row>
@@ -4249,12 +4249,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>18035</t>
+          <t>17663</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>37107</t>
+          <t>36666</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4264,12 +4264,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>13057</t>
+          <t>13307</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>26127</t>
+          <t>25814</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>34910</t>
+          <t>34144</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>58915</t>
+          <t>58078</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4334,12 +4334,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -4362,12 +4362,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>70554</t>
+          <t>69354</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>102899</t>
+          <t>103571</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4377,12 +4377,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>69739</t>
+          <t>69738</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>94534</t>
+          <t>94810</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>146106</t>
+          <t>147609</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>190536</t>
+          <t>188873</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,08%</t>
         </is>
       </c>
     </row>
@@ -4475,12 +4475,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>387114</t>
+          <t>389962</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>426378</t>
+          <t>430911</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4490,12 +4490,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>69,71%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>76,22%</t>
+          <t>77,03%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4510,12 +4510,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>394137</t>
+          <t>391830</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>423970</t>
+          <t>424051</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>71,69%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>77,59%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>793079</t>
+          <t>792280</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>845118</t>
+          <t>841967</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>71,64%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>76,42%</t>
+          <t>76,13%</t>
         </is>
       </c>
     </row>
@@ -4710,7 +4710,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>5322</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>5413</t>
+          <t>5175</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>7496</t>
+          <t>7677</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -4818,12 +4818,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>10748</t>
+          <t>11033</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4833,12 +4833,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4853,12 +4853,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>537</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>6250</t>
+          <t>6518</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>3271</t>
+          <t>3559</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>14567</t>
+          <t>14338</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -4931,12 +4931,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>15054</t>
+          <t>14615</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>29587</t>
+          <t>29437</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4946,12 +4946,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4966,12 +4966,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>8136</t>
+          <t>7216</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>33106</t>
+          <t>33836</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4981,12 +4981,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>19960</t>
+          <t>20449</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>56526</t>
+          <t>56452</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5016,12 +5016,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,79%</t>
         </is>
       </c>
     </row>
@@ -5044,12 +5044,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>8995</t>
+          <t>9436</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>21307</t>
+          <t>21884</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5059,12 +5059,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5079,12 +5079,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>3063</t>
+          <t>3369</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>18393</t>
+          <t>17908</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5094,12 +5094,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5114,12 +5114,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>11798</t>
+          <t>10996</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>34604</t>
+          <t>34782</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -5157,12 +5157,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>11115</t>
+          <t>11165</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>24689</t>
+          <t>24841</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5172,12 +5172,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5192,12 +5192,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>7933</t>
+          <t>7437</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>35137</t>
+          <t>35217</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5207,12 +5207,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5227,12 +5227,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>18375</t>
+          <t>19429</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>52834</t>
+          <t>53666</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5242,12 +5242,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -5270,12 +5270,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>295819</t>
+          <t>294192</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>318664</t>
+          <t>317888</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5285,12 +5285,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>80,08%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>86,53%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5305,12 +5305,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>519098</t>
+          <t>519613</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>585676</t>
+          <t>585266</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5320,12 +5320,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5340,12 +5340,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>824465</t>
+          <t>823954</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>921651</t>
+          <t>916993</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5355,12 +5355,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,04%</t>
         </is>
       </c>
     </row>
@@ -5505,7 +5505,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>5552</t>
+          <t>4141</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5535,12 +5535,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>1735</t>
+          <t>1440</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>7820</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5550,12 +5550,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5570,12 +5570,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>2167</t>
+          <t>2060</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>9821</t>
+          <t>8813</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5585,12 +5585,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -5618,7 +5618,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>3389</t>
+          <t>2436</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5633,7 +5633,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5648,12 +5648,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>1572</t>
+          <t>1760</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>7411</t>
+          <t>7717</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5663,12 +5663,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5683,12 +5683,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>2116</t>
+          <t>2124</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>8209</t>
+          <t>8128</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5703,7 +5703,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -5726,12 +5726,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>6151</t>
+          <t>6099</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>16640</t>
+          <t>17210</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5761,12 +5761,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>4256</t>
+          <t>4143</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>12106</t>
+          <t>12043</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5776,12 +5776,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>12225</t>
+          <t>11717</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>25393</t>
+          <t>25017</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5811,12 +5811,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -5839,12 +5839,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>1349</t>
+          <t>1430</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>8157</t>
+          <t>7922</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5874,12 +5874,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>9512</t>
+          <t>9762</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>19689</t>
+          <t>20050</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5889,12 +5889,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5909,12 +5909,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>12041</t>
+          <t>12918</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>24153</t>
+          <t>25063</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5924,12 +5924,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -5952,12 +5952,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>1894</t>
+          <t>1946</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>9228</t>
+          <t>8709</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5987,12 +5987,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>4490</t>
+          <t>4583</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>12500</t>
+          <t>12612</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6002,12 +6002,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6022,12 +6022,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>7970</t>
+          <t>7774</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>18762</t>
+          <t>18364</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -6065,12 +6065,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>254636</t>
+          <t>254960</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>268063</t>
+          <t>268907</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6080,12 +6080,12 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6100,12 +6100,12 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>377865</t>
+          <t>379152</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>395506</t>
+          <t>395389</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6135,12 +6135,12 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>637413</t>
+          <t>640188</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>659604</t>
+          <t>660423</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,35%</t>
         </is>
       </c>
     </row>
@@ -6295,12 +6295,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>17616</t>
+          <t>17959</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>52531</t>
+          <t>57827</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6310,12 +6310,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6330,12 +6330,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>15083</t>
+          <t>15216</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>36390</t>
+          <t>36674</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6365,12 +6365,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>39112</t>
+          <t>37965</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>79225</t>
+          <t>78140</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6380,12 +6380,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -6408,12 +6408,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>39627</t>
+          <t>39230</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>76586</t>
+          <t>75573</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6423,12 +6423,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6443,12 +6443,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>36734</t>
+          <t>37978</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>63766</t>
+          <t>65679</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6458,12 +6458,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6478,12 +6478,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>83883</t>
+          <t>83018</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>128472</t>
+          <t>129157</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6493,12 +6493,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -6521,12 +6521,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>256410</t>
+          <t>267033</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>387848</t>
+          <t>392469</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6536,12 +6536,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6556,12 +6556,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>340228</t>
+          <t>339552</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>712779</t>
+          <t>692543</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6571,12 +6571,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6591,12 +6591,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>667054</t>
+          <t>661637</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>1046314</t>
+          <t>1017651</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,27%</t>
         </is>
       </c>
     </row>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>131457</t>
+          <t>128722</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>206495</t>
+          <t>206914</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6649,12 +6649,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6669,12 +6669,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>107363</t>
+          <t>107086</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>156850</t>
+          <t>159616</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6689,7 +6689,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>260405</t>
+          <t>256461</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>350632</t>
+          <t>346746</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -6747,12 +6747,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>637886</t>
+          <t>637056</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>890894</t>
+          <t>899659</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6762,12 +6762,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6782,12 +6782,12 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>684918</t>
+          <t>651829</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>901030</t>
+          <t>906038</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>1397476</t>
+          <t>1391446</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>1771538</t>
+          <t>1756155</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,62%</t>
         </is>
       </c>
     </row>
@@ -6860,12 +6860,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>1903297</t>
+          <t>1897379</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>2344781</t>
+          <t>2328557</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -6875,12 +6875,12 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>55,24%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>67,79%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6895,12 +6895,12 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>2064087</t>
+          <t>2077064</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>2481545</t>
+          <t>2508919</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>56,16%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>67,83%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>4002936</t>
+          <t>4027311</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>4603104</t>
+          <t>4626237</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>56,11%</t>
+          <t>56,46%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>64,53%</t>
+          <t>64,85%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P04A_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P04A_2023-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>11521</t>
+          <t>11157</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3540</t>
+          <t>3377</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31606</t>
+          <t>29943</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4627</t>
+          <t>4910</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17149</t>
+          <t>16438</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>16148</t>
+          <t>16067</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6450</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35328</t>
+          <t>40864</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,42%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7547</t>
+          <t>6844</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1549</t>
+          <t>1511</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23804</t>
+          <t>22532</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,27 +873,27 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7266</t>
+          <t>7784</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2953</t>
+          <t>3244</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14965</t>
+          <t>17317</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>14814</t>
+          <t>14628</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6846</t>
+          <t>6457</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>32551</t>
+          <t>28397</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>31769</t>
+          <t>63687</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18794</t>
+          <t>42136</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>52252</t>
+          <t>89652</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>62307</t>
+          <t>89269</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>45491</t>
+          <t>65692</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>86031</t>
+          <t>111284</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>94076</t>
+          <t>152956</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>70754</t>
+          <t>120863</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>123023</t>
+          <t>191504</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>25,39%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>28122</t>
+          <t>22582</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13057</t>
+          <t>11462</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55378</t>
+          <t>40948</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>10709</t>
+          <t>10794</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3559</t>
+          <t>4675</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21480</t>
+          <t>21883</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>38830</t>
+          <t>33376</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22894</t>
+          <t>19771</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>62659</t>
+          <t>55429</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>7,35%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>98107</t>
+          <t>93676</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>71613</t>
+          <t>69175</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>131093</t>
+          <t>125524</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>71332</t>
+          <t>78401</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>52874</t>
+          <t>59425</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>91617</t>
+          <t>100379</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>169439</t>
+          <t>172076</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>136740</t>
+          <t>140947</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>206464</t>
+          <t>209590</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>27,78%</t>
         </is>
       </c>
     </row>
@@ -1290,32 +1290,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>207079</t>
+          <t>195562</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>175975</t>
+          <t>163972</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>239282</t>
+          <t>227519</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>49,7%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>45,81%</t>
+          <t>41,67%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>62,29%</t>
+          <t>57,82%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1325,32 +1325,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>155349</t>
+          <t>169664</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>130564</t>
+          <t>143371</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>178089</t>
+          <t>198455</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>47,02%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>41,9%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>57,15%</t>
+          <t>55,0%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>362428</t>
+          <t>365225</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>322851</t>
+          <t>321386</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>404686</t>
+          <t>407798</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>48,42%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>46,4%</t>
+          <t>42,61%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>54,06%</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>384146</t>
+          <t>393507</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>384146</t>
+          <t>393507</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>384146</t>
+          <t>393507</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,17 +1438,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>311590</t>
+          <t>360821</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>311590</t>
+          <t>360821</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>311590</t>
+          <t>360821</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,17 +1473,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>695736</t>
+          <t>754328</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>695736</t>
+          <t>754328</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>695736</t>
+          <t>754328</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6701</t>
+          <t>9324</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1678</t>
+          <t>2960</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19741</t>
+          <t>23121</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3208</t>
+          <t>4196</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>803</t>
+          <t>1123</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9098</t>
+          <t>10134</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>9909</t>
+          <t>13520</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3811</t>
+          <t>6781</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>21060</t>
+          <t>27301</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>12596</t>
+          <t>15744</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6311</t>
+          <t>8354</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>22766</t>
+          <t>26756</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>10853</t>
+          <t>12580</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4880</t>
+          <t>6698</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21745</t>
+          <t>23588</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>23449</t>
+          <t>28324</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>14358</t>
+          <t>18009</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>37534</t>
+          <t>44655</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>96964</t>
+          <t>125983</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>76181</t>
+          <t>101279</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>120469</t>
+          <t>154035</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>159943</t>
+          <t>121719</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>98913</t>
+          <t>102655</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>297086</t>
+          <t>143706</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>58,28%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>256908</t>
+          <t>247702</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>194855</t>
+          <t>215916</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>431508</t>
+          <t>280899</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>28,86%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>32603</t>
+          <t>30468</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>19984</t>
+          <t>18611</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>49700</t>
+          <t>47234</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>31354</t>
+          <t>30250</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18526</t>
+          <t>21004</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>45624</t>
+          <t>41855</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,22 +1929,22 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>63957</t>
+          <t>60718</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>43652</t>
+          <t>45520</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>85491</t>
+          <t>81840</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>8,41%</t>
         </is>
       </c>
     </row>
@@ -1972,32 +1972,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>126323</t>
+          <t>131508</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>103370</t>
+          <t>106770</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>150503</t>
+          <t>156429</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2007,32 +2007,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>141722</t>
+          <t>152767</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>89781</t>
+          <t>131001</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>171671</t>
+          <t>173390</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,32 +2042,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>268045</t>
+          <t>284275</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>200014</t>
+          <t>250683</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>305831</t>
+          <t>317292</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>32,6%</t>
         </is>
       </c>
     </row>
@@ -2085,32 +2085,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>146832</t>
+          <t>162213</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>124107</t>
+          <t>136952</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>172061</t>
+          <t>191086</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>40,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2120,32 +2120,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>162683</t>
+          <t>176652</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>96171</t>
+          <t>155016</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>198665</t>
+          <t>200037</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,32 +2155,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>309515</t>
+          <t>338864</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>225550</t>
+          <t>301145</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>348320</t>
+          <t>371796</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>38,2%</t>
         </is>
       </c>
     </row>
@@ -2198,17 +2198,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>422020</t>
+          <t>475239</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>422020</t>
+          <t>475239</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>422020</t>
+          <t>475239</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,17 +2233,17 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>509762</t>
+          <t>498164</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>509762</t>
+          <t>498164</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>509762</t>
+          <t>498164</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,17 +2268,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>931782</t>
+          <t>973403</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>931782</t>
+          <t>973403</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>931782</t>
+          <t>973403</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4038</t>
+          <t>3926</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>1080</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11070</t>
+          <t>10098</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4005</t>
+          <t>4576</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1551</t>
+          <t>1767</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9358</t>
+          <t>10794</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>8042</t>
+          <t>8502</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3478</t>
+          <t>4069</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>16021</t>
+          <t>16594</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>15250</t>
+          <t>16658</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8845</t>
+          <t>10308</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24037</t>
+          <t>26770</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>10597</t>
+          <t>11615</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5744</t>
+          <t>6801</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17171</t>
+          <t>18212</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>25847</t>
+          <t>28273</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17948</t>
+          <t>19925</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>37237</t>
+          <t>40218</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>78064</t>
+          <t>136804</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>62740</t>
+          <t>115137</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>98561</t>
+          <t>160257</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>120275</t>
+          <t>107009</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>72862</t>
+          <t>90868</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>242644</t>
+          <t>124220</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>41,13%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>198340</t>
+          <t>243813</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>148702</t>
+          <t>217745</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>335105</t>
+          <t>270312</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>21,86%</t>
         </is>
       </c>
     </row>
@@ -2654,32 +2654,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>35943</t>
+          <t>35433</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>25357</t>
+          <t>25463</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>50397</t>
+          <t>49347</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2689,32 +2689,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>25208</t>
+          <t>25568</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>16515</t>
+          <t>18453</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>35090</t>
+          <t>35118</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2724,32 +2724,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>61151</t>
+          <t>61001</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>46499</t>
+          <t>47215</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>75910</t>
+          <t>77392</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,26%</t>
         </is>
       </c>
     </row>
@@ -2767,32 +2767,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>253597</t>
+          <t>265870</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>231439</t>
+          <t>241077</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>276578</t>
+          <t>291874</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>43,19%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>47,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2802,32 +2802,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>270859</t>
+          <t>294615</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>196840</t>
+          <t>274253</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>301627</t>
+          <t>315923</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>47,44%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>44,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>51,13%</t>
+          <t>50,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2837,32 +2837,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>524456</t>
+          <t>560485</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>446589</t>
+          <t>525938</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>563267</t>
+          <t>593673</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>46,77%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>42,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>48,01%</t>
         </is>
       </c>
     </row>
@@ -2880,32 +2880,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>144476</t>
+          <t>156909</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>124266</t>
+          <t>133850</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>164793</t>
+          <t>181497</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2915,32 +2915,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>158941</t>
+          <t>177598</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>118979</t>
+          <t>159969</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>181819</t>
+          <t>198288</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2950,32 +2950,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>303417</t>
+          <t>334507</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>258218</t>
+          <t>305303</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>335110</t>
+          <t>363432</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>29,39%</t>
         </is>
       </c>
     </row>
@@ -2993,17 +2993,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>531368</t>
+          <t>615599</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>531368</t>
+          <t>615599</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>531368</t>
+          <t>615599</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,17 +3028,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>589885</t>
+          <t>620982</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>589885</t>
+          <t>620982</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>589885</t>
+          <t>620982</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,17 +3063,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1121253</t>
+          <t>1236581</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1121253</t>
+          <t>1236581</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1121253</t>
+          <t>1236581</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>5094</t>
+          <t>8145</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1126</t>
+          <t>2926</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>14134</t>
+          <t>19134</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>4430</t>
+          <t>6715</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2055</t>
+          <t>3388</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8238</t>
+          <t>11757</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>9524</t>
+          <t>14860</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4213</t>
+          <t>8808</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>18320</t>
+          <t>25599</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -3223,69 +3223,69 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>8586</t>
+          <t>10296</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>5145</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>17811</t>
+          <t>18693</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
+          <t>2,67%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>8731</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>5162</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>14699</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
           <t>2,01%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>8310</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>4491</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>14164</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>2,0%</t>
-        </is>
-      </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>24</t>
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>16897</t>
+          <t>19027</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>8720</t>
+          <t>12385</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>26084</t>
+          <t>28266</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -3336,32 +3336,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>67088</t>
+          <t>85240</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>25337</t>
+          <t>69986</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>102970</t>
+          <t>105759</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3371,32 +3371,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>52530</t>
+          <t>64367</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>39843</t>
+          <t>53210</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>72184</t>
+          <t>77918</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3406,32 +3406,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>119617</t>
+          <t>149607</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>74499</t>
+          <t>128752</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>159317</t>
+          <t>172987</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>12,07%</t>
         </is>
       </c>
     </row>
@@ -3449,32 +3449,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>28978</t>
+          <t>28408</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>12246</t>
+          <t>18842</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>47231</t>
+          <t>39634</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3484,32 +3484,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>25064</t>
+          <t>26827</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>18121</t>
+          <t>20045</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>33737</t>
+          <t>35458</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3519,32 +3519,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>54042</t>
+          <t>55235</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>31863</t>
+          <t>41810</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>70750</t>
+          <t>70014</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,89%</t>
         </is>
       </c>
     </row>
@@ -3562,32 +3562,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>226342</t>
+          <t>237774</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>99361</t>
+          <t>212711</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>323545</t>
+          <t>264484</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3597,32 +3597,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>235803</t>
+          <t>253129</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>198113</t>
+          <t>231572</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>258643</t>
+          <t>273454</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>37,35%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3632,32 +3632,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>462145</t>
+          <t>490904</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>274364</t>
+          <t>455829</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>559219</t>
+          <t>525043</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>36,64%</t>
         </is>
       </c>
     </row>
@@ -3675,32 +3675,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>551698</t>
+          <t>330754</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>413505</t>
+          <t>304071</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>743521</t>
+          <t>356758</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>47,21%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>43,4%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>50,92%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3710,32 +3710,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>382308</t>
+          <t>372437</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>356433</t>
+          <t>349528</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>429311</t>
+          <t>394571</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>53,96%</t>
+          <t>50,87%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>47,74%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>60,6%</t>
+          <t>53,89%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3745,32 +3745,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>934006</t>
+          <t>703191</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>798786</t>
+          <t>670307</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1194539</t>
+          <t>737529</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>58,51%</t>
+          <t>49,08%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>50,04%</t>
+          <t>46,78%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>51,47%</t>
         </is>
       </c>
     </row>
@@ -3788,17 +3788,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3823,17 +3823,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>708446</t>
+          <t>732206</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>708446</t>
+          <t>732206</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>708446</t>
+          <t>732206</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3858,17 +3858,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>1596232</t>
+          <t>1432823</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1596232</t>
+          <t>1432823</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1596232</t>
+          <t>1432823</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>2502</t>
+          <t>4139</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>990</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>8969</t>
+          <t>10906</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>1205</t>
+          <t>1701</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>406</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3638</t>
+          <t>5425</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>5840</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>9397</t>
+          <t>14039</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -4018,32 +4018,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>5728</t>
+          <t>6907</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>3275</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>11230</t>
+          <t>13511</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4053,32 +4053,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>6735</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>3777</t>
+          <t>3772</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>11688</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4088,32 +4088,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>12463</t>
+          <t>14184</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>7196</t>
+          <t>8557</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>18836</t>
+          <t>21326</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -4131,32 +4131,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>31490</t>
+          <t>47052</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>21951</t>
+          <t>35230</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>42159</t>
+          <t>59839</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4166,32 +4166,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>28806</t>
+          <t>40405</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>21560</t>
+          <t>31517</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>36998</t>
+          <t>51306</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4201,32 +4201,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>60296</t>
+          <t>87458</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>48829</t>
+          <t>72730</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>73534</t>
+          <t>106380</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>8,76%</t>
         </is>
       </c>
     </row>
@@ -4244,32 +4244,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>26387</t>
+          <t>26533</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>17663</t>
+          <t>18330</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>36666</t>
+          <t>36941</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4279,32 +4279,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>18707</t>
+          <t>19551</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>13307</t>
+          <t>13581</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>25814</t>
+          <t>26305</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4314,32 +4314,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>45094</t>
+          <t>46084</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>34144</t>
+          <t>35584</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>58078</t>
+          <t>58872</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -4357,32 +4357,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>85465</t>
+          <t>86709</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>69354</t>
+          <t>70415</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>103571</t>
+          <t>103985</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4392,32 +4392,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>81660</t>
+          <t>89851</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>69738</t>
+          <t>77032</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>94810</t>
+          <t>105247</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4427,32 +4427,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>167125</t>
+          <t>176560</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>147609</t>
+          <t>155764</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>188873</t>
+          <t>197385</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>16,25%</t>
         </is>
       </c>
     </row>
@@ -4470,32 +4470,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>407853</t>
+          <t>436241</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>389962</t>
+          <t>416175</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>430911</t>
+          <t>458685</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>72,91%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>69,71%</t>
+          <t>68,5%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>77,03%</t>
+          <t>75,49%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4505,67 +4505,67 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>409412</t>
+          <t>448166</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>391830</t>
+          <t>431765</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>424051</t>
+          <t>465332</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
+          <t>73,84%</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>71,14%</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>76,67%</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>1225</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>884407</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>855572</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>909771</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>72,82%</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>70,44%</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
           <t>74,91%</t>
-        </is>
-      </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>71,69%</t>
-        </is>
-      </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>77,59%</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>1225</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t>817265</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t>792280</t>
-        </is>
-      </c>
-      <c r="T37" s="2" t="inlineStr">
-        <is>
-          <t>841967</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t>73,9%</t>
-        </is>
-      </c>
-      <c r="V37" s="2" t="inlineStr">
-        <is>
-          <t>71,64%</t>
-        </is>
-      </c>
-      <c r="W37" s="2" t="inlineStr">
-        <is>
-          <t>76,13%</t>
         </is>
       </c>
     </row>
@@ -4583,17 +4583,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>559424</t>
+          <t>607582</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>559424</t>
+          <t>607582</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>559424</t>
+          <t>607582</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4618,17 +4618,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>546525</t>
+          <t>606951</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>546525</t>
+          <t>606951</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>546525</t>
+          <t>606951</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4653,17 +4653,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>1105949</t>
+          <t>1214533</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1105949</t>
+          <t>1214533</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1105949</t>
+          <t>1214533</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4700,7 +4700,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>1445</t>
+          <t>1498</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>5541</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4735,32 +4735,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>1958</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>981</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>5175</t>
+          <t>5767</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4770,32 +4770,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>3403</t>
+          <t>3649</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>1598</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>7677</t>
+          <t>8187</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -4813,17 +4813,17 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>5533</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2739</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>11033</t>
+          <t>11553</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4838,7 +4838,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4848,32 +4848,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>2586</t>
+          <t>2813</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>537</t>
+          <t>1086</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>6518</t>
+          <t>6414</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4883,32 +4883,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>8119</t>
+          <t>8960</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>3559</t>
+          <t>4617</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>14338</t>
+          <t>15308</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -4926,32 +4926,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>21234</t>
+          <t>27155</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>14615</t>
+          <t>19163</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>29437</t>
+          <t>36229</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4961,32 +4961,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>19985</t>
+          <t>24477</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>7216</t>
+          <t>18029</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>33836</t>
+          <t>32195</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4996,32 +4996,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>41219</t>
+          <t>51632</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>20449</t>
+          <t>41669</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>56452</t>
+          <t>64301</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>7,61%</t>
         </is>
       </c>
     </row>
@@ -5039,32 +5039,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>14517</t>
+          <t>15366</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>9436</t>
+          <t>9665</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>21884</t>
+          <t>23149</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5074,32 +5074,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>9859</t>
+          <t>10042</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>3369</t>
+          <t>6069</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>17908</t>
+          <t>15797</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5109,32 +5109,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>24376</t>
+          <t>25409</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>10996</t>
+          <t>18371</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>34782</t>
+          <t>34716</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -5152,32 +5152,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>17066</t>
+          <t>19454</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>11165</t>
+          <t>12993</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>24841</t>
+          <t>27704</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5187,32 +5187,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>21349</t>
+          <t>23428</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>7437</t>
+          <t>17087</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>35217</t>
+          <t>32043</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5222,32 +5222,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>38415</t>
+          <t>42882</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>19429</t>
+          <t>33071</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>53666</t>
+          <t>54737</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>6,48%</t>
         </is>
       </c>
     </row>
@@ -5265,32 +5265,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>307589</t>
+          <t>336606</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>294192</t>
+          <t>323356</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>317888</t>
+          <t>348895</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>79,6%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5300,32 +5300,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>552039</t>
+          <t>375576</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>519613</t>
+          <t>364514</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>585266</t>
+          <t>386380</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>85,65%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>83,13%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5335,32 +5335,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>859628</t>
+          <t>712182</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>823954</t>
+          <t>693271</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>916993</t>
+          <t>727169</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>82,07%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>86,08%</t>
         </is>
       </c>
     </row>
@@ -5378,17 +5378,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>367384</t>
+          <t>406227</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>367384</t>
+          <t>406227</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>367384</t>
+          <t>406227</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5413,17 +5413,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>607775</t>
+          <t>438487</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>607775</t>
+          <t>438487</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>607775</t>
+          <t>438487</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5448,17 +5448,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>975160</t>
+          <t>844713</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>975160</t>
+          <t>844713</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>975160</t>
+          <t>844713</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5495,7 +5495,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>906</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -5505,7 +5505,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>4141</t>
+          <t>4510</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5530,32 +5530,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>3961</t>
+          <t>4446</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>1440</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>7820</t>
+          <t>9540</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5565,32 +5565,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>4779</t>
+          <t>5353</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>2060</t>
+          <t>2127</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>8813</t>
+          <t>10603</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -5608,7 +5608,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>993</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -5618,12 +5618,12 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>2436</t>
+          <t>3673</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -5633,7 +5633,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5643,32 +5643,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>3800</t>
+          <t>4416</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>1760</t>
+          <t>1798</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>7717</t>
+          <t>7996</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5678,32 +5678,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>4433</t>
+          <t>5409</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>2124</t>
+          <t>2691</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>8128</t>
+          <t>9193</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -5721,32 +5721,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>10535</t>
+          <t>12491</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>6099</t>
+          <t>7383</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>17210</t>
+          <t>19113</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5756,32 +5756,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>7174</t>
+          <t>8880</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>4143</t>
+          <t>5586</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>12043</t>
+          <t>15056</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5791,32 +5791,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>17710</t>
+          <t>21371</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>11717</t>
+          <t>14615</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>25017</t>
+          <t>30176</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -5834,32 +5834,32 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>3759</t>
+          <t>4175</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>1430</t>
+          <t>1611</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>7922</t>
+          <t>9012</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5869,32 +5869,32 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>14113</t>
+          <t>14862</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>9762</t>
+          <t>10294</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>20050</t>
+          <t>21268</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5904,32 +5904,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>17872</t>
+          <t>19037</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>12918</t>
+          <t>13218</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>25063</t>
+          <t>26755</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -5947,22 +5947,22 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>4512</t>
+          <t>5062</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>1946</t>
+          <t>2133</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>8709</t>
+          <t>9740</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -5972,77 +5972,77 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
+          <t>3,14%</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>9220</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>5471</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>14293</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>1,99%</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>1,18%</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
           <t>3,08%</t>
         </is>
       </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>7865</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="inlineStr">
-        <is>
-          <t>4583</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr">
-        <is>
-          <t>12612</t>
-        </is>
-      </c>
-      <c r="N50" s="2" t="inlineStr">
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr">
+        <is>
+          <t>14282</t>
+        </is>
+      </c>
+      <c r="S50" s="2" t="inlineStr">
+        <is>
+          <t>9386</t>
+        </is>
+      </c>
+      <c r="T50" s="2" t="inlineStr">
+        <is>
+          <t>21564</t>
+        </is>
+      </c>
+      <c r="U50" s="2" t="inlineStr">
         <is>
           <t>1,85%</t>
         </is>
       </c>
-      <c r="O50" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="P50" s="2" t="inlineStr">
-        <is>
-          <t>2,97%</t>
-        </is>
-      </c>
-      <c r="Q50" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="R50" s="2" t="inlineStr">
-        <is>
-          <t>12376</t>
-        </is>
-      </c>
-      <c r="S50" s="2" t="inlineStr">
-        <is>
-          <t>7774</t>
-        </is>
-      </c>
-      <c r="T50" s="2" t="inlineStr">
-        <is>
-          <t>18364</t>
-        </is>
-      </c>
-      <c r="U50" s="2" t="inlineStr">
-        <is>
-          <t>1,75%</t>
-        </is>
-      </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -6060,32 +6060,32 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>262502</t>
+          <t>286572</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>254960</t>
+          <t>277302</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>268907</t>
+          <t>293521</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6095,32 +6095,32 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>387811</t>
+          <t>421651</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>379152</t>
+          <t>410323</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>395389</t>
+          <t>429530</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6130,32 +6130,32 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>650313</t>
+          <t>708224</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>640188</t>
+          <t>694001</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>660423</t>
+          <t>718709</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>92,9%</t>
         </is>
       </c>
     </row>
@@ -6173,17 +6173,17 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6208,17 +6208,17 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>424724</t>
+          <t>463476</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>424724</t>
+          <t>463476</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>424724</t>
+          <t>463476</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6243,17 +6243,17 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>707483</t>
+          <t>773675</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>707483</t>
+          <t>773675</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>707483</t>
+          <t>773675</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6290,102 +6290,102 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>32120</t>
+          <t>39095</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>17959</t>
+          <t>24968</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>57827</t>
+          <t>62564</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>1,78%</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>28695</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>19262</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>41562</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>1,12%</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr">
+        <is>
+          <t>67790</t>
+        </is>
+      </c>
+      <c r="S53" s="2" t="inlineStr">
+        <is>
+          <t>48737</t>
+        </is>
+      </c>
+      <c r="T53" s="2" t="inlineStr">
+        <is>
+          <t>92877</t>
+        </is>
+      </c>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
           <t>0,94%</t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>1,68%</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t>23392</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="inlineStr">
-        <is>
-          <t>15216</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr">
-        <is>
-          <t>36674</t>
-        </is>
-      </c>
-      <c r="N53" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="O53" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="P53" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
-      <c r="Q53" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="R53" s="2" t="inlineStr">
-        <is>
-          <t>55512</t>
-        </is>
-      </c>
-      <c r="S53" s="2" t="inlineStr">
-        <is>
-          <t>37965</t>
-        </is>
-      </c>
-      <c r="T53" s="2" t="inlineStr">
-        <is>
-          <t>78140</t>
-        </is>
-      </c>
-      <c r="U53" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -6403,67 +6403,67 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>55872</t>
+          <t>63589</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>39230</t>
+          <t>48329</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>75573</t>
+          <t>83436</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>2,38%</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>55216</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>42578</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>70146</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
           <t>1,14%</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>2,2%</t>
-        </is>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="K54" s="2" t="inlineStr">
-        <is>
-          <t>50149</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="inlineStr">
-        <is>
-          <t>37978</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr">
-        <is>
-          <t>65679</t>
-        </is>
-      </c>
-      <c r="N54" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
-      <c r="O54" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
-        </is>
-      </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6473,32 +6473,32 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>106021</t>
+          <t>118804</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>83018</t>
+          <t>99346</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>129157</t>
+          <t>142069</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -6516,32 +6516,32 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>337144</t>
+          <t>498412</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>267033</t>
+          <t>448695</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>392469</t>
+          <t>547089</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6551,32 +6551,32 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>451021</t>
+          <t>456126</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>339552</t>
+          <t>418028</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>692543</t>
+          <t>493718</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6586,32 +6586,32 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>788165</t>
+          <t>954538</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>661637</t>
+          <t>891772</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>1017651</t>
+          <t>1019000</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,09%</t>
         </is>
       </c>
     </row>
@@ -6629,32 +6629,32 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>170309</t>
+          <t>162964</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>128722</t>
+          <t>135264</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>206914</t>
+          <t>192107</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6664,32 +6664,32 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>135013</t>
+          <t>137895</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>107086</t>
+          <t>118556</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>159616</t>
+          <t>158985</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6699,32 +6699,32 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>305322</t>
+          <t>300859</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>256461</t>
+          <t>265254</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>346746</t>
+          <t>335113</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,63%</t>
         </is>
       </c>
     </row>
@@ -6742,32 +6742,32 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>811412</t>
+          <t>840053</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>637056</t>
+          <t>782188</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>899659</t>
+          <t>900527</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6777,32 +6777,32 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>830589</t>
+          <t>901411</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>651829</t>
+          <t>852137</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>906038</t>
+          <t>947552</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6812,32 +6812,32 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>1642001</t>
+          <t>1741464</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>1391446</t>
+          <t>1670810</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>1756155</t>
+          <t>1818976</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>25,16%</t>
         </is>
       </c>
     </row>
@@ -6855,32 +6855,32 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>2028030</t>
+          <t>1904856</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>1897379</t>
+          <t>1839438</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>2328557</t>
+          <t>1970047</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>59,04%</t>
+          <t>54,29%</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>55,24%</t>
+          <t>52,42%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>56,14%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6890,32 +6890,32 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>2208544</t>
+          <t>2141743</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>2077064</t>
+          <t>2088751</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>2508919</t>
+          <t>2197717</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>57,56%</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>56,16%</t>
+          <t>56,13%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>59,06%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6925,32 +6925,32 @@
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
-          <t>4236574</t>
+          <t>4046600</t>
         </is>
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>4027311</t>
+          <t>3961917</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>4626237</t>
+          <t>4131355</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
         <is>
-          <t>59,39%</t>
+          <t>55,97%</t>
         </is>
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>56,46%</t>
+          <t>54,8%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>64,85%</t>
+          <t>57,14%</t>
         </is>
       </c>
     </row>
@@ -6968,17 +6968,17 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>3434888</t>
+          <t>3508969</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>3434888</t>
+          <t>3508969</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>3434888</t>
+          <t>3508969</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -7003,17 +7003,17 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>3698708</t>
+          <t>3721087</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>3698708</t>
+          <t>3721087</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>3698708</t>
+          <t>3721087</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7038,17 +7038,17 @@
       </c>
       <c r="R59" s="2" t="inlineStr">
         <is>
-          <t>7133596</t>
+          <t>7230056</t>
         </is>
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>7133596</t>
+          <t>7230056</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>7133596</t>
+          <t>7230056</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
